--- a/results/VI and heur scores.xlsx
+++ b/results/VI and heur scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\research\umich\mpt\pilot\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34248C1A-3362-4093-A8BA-80AABBDE5712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB79FEAC-EB08-41EA-B365-51C487C92439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{2FE0DFFB-5825-496F-895C-1859655CAA03}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2FE0DFFB-5825-496F-895C-1859655CAA03}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>central_adj</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>Monte Carlo</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>VI fixed b</t>
   </si>
 </sst>
 </file>
@@ -437,137 +443,213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7E96E1-0FC4-40D4-A09A-CDB2A6C587CB}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" t="s">
         <v>2</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>1</v>
-      </c>
-      <c r="B3">
-        <v>1.2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>5.46</v>
-      </c>
-      <c r="E3">
-        <v>3.72</v>
-      </c>
-      <c r="F3">
-        <v>3.74</v>
-      </c>
-      <c r="G3">
-        <v>5.39</v>
-      </c>
-      <c r="I3">
-        <v>3.72</v>
-      </c>
-      <c r="J3">
-        <v>5.39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>4</v>
       </c>
       <c r="B4">
         <v>1.2</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>1.86</v>
+        <v>5.46</v>
       </c>
       <c r="E4">
-        <v>1.41</v>
+        <v>3.72</v>
       </c>
       <c r="F4">
-        <v>1.42</v>
+        <v>3.74</v>
       </c>
       <c r="G4">
-        <v>1.78</v>
+        <v>5.39</v>
+      </c>
+      <c r="H4">
+        <v>5.48</v>
       </c>
       <c r="I4">
-        <v>1.42</v>
-      </c>
-      <c r="J4">
-        <v>1.8</v>
+        <v>5.44</v>
+      </c>
+      <c r="K4">
+        <v>3.72</v>
+      </c>
+      <c r="L4">
+        <v>5.39</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>1.2</v>
       </c>
       <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>3.75</v>
+      </c>
+      <c r="E5">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="F5">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="G5">
+        <v>3.75</v>
+      </c>
+      <c r="H5">
+        <v>3.78</v>
+      </c>
+      <c r="I5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1.2</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="E6">
+        <v>1.8</v>
+      </c>
+      <c r="F6">
+        <v>1.8</v>
+      </c>
+      <c r="G6">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="H6">
+        <v>2.61</v>
+      </c>
+      <c r="I6">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>1.2</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>1.86</v>
+      </c>
+      <c r="E7">
+        <v>1.41</v>
+      </c>
+      <c r="F7">
+        <v>1.42</v>
+      </c>
+      <c r="G7">
+        <v>1.78</v>
+      </c>
+      <c r="H7">
+        <v>2.06</v>
+      </c>
+      <c r="I7">
+        <v>2.02</v>
+      </c>
+      <c r="K7">
+        <v>1.42</v>
+      </c>
+      <c r="L7">
+        <v>1.8</v>
+      </c>
+      <c r="N7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>1.2</v>
+      </c>
+      <c r="C8">
         <v>50</v>
       </c>
-      <c r="D5">
+      <c r="D8">
         <v>1.46</v>
       </c>
-      <c r="E5">
+      <c r="E8">
         <v>1.02</v>
       </c>
-      <c r="F5">
+      <c r="F8">
         <v>1.1599999999999999</v>
       </c>
-      <c r="G5">
+      <c r="G8">
         <v>1.42</v>
       </c>
-      <c r="I5">
+      <c r="K8">
         <v>0.97</v>
       </c>
-      <c r="J5">
+      <c r="L8">
         <v>0.96899999999999997</v>
-      </c>
-      <c r="L5" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/results/VI and heur scores.xlsx
+++ b/results/VI and heur scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\research\umich\mpt\pilot\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB79FEAC-EB08-41EA-B365-51C487C92439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22561727-6244-48B1-9AD5-C6D58976B479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2FE0DFFB-5825-496F-895C-1859655CAA03}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>central_adj</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>VI fixed b</t>
+  </si>
+  <si>
+    <t>sigma</t>
   </si>
 </sst>
 </file>
@@ -443,13 +446,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7E96E1-0FC4-40D4-A09A-CDB2A6C587CB}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
         <v>9</v>
       </c>
@@ -457,198 +460,216 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>10</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>11</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>2</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4">
+        <v>0.2</v>
+      </c>
+      <c r="C4">
         <v>1.2</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>5.46</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>3.72</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>3.74</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>5.39</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>5.48</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>5.44</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>3.72</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>5.39</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5">
+        <v>0.2</v>
+      </c>
+      <c r="C5">
         <v>1.2</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>5</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>3.75</v>
-      </c>
-      <c r="E5">
-        <v>2.5299999999999998</v>
       </c>
       <c r="F5">
         <v>2.5299999999999998</v>
       </c>
       <c r="G5">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="H5">
         <v>3.75</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>3.78</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>3.75</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6">
+        <v>0.2</v>
+      </c>
+      <c r="C6">
         <v>1.2</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>10</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>2.5299999999999998</v>
-      </c>
-      <c r="E6">
-        <v>1.8</v>
       </c>
       <c r="F6">
         <v>1.8</v>
       </c>
       <c r="G6">
+        <v>1.8</v>
+      </c>
+      <c r="H6">
         <v>2.5299999999999998</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>2.61</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>2.6</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7">
+        <v>0.2</v>
+      </c>
+      <c r="C7">
         <v>1.2</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>20</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>1.86</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>1.41</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>1.42</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1.78</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>2.06</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>2.02</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1.42</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>1.8</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8">
+        <v>0.2</v>
+      </c>
+      <c r="C8">
         <v>1.2</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>50</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1.46</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>1.02</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>1.1599999999999999</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1.42</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.97</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.96899999999999997</v>
       </c>
     </row>

--- a/results/VI and heur scores.xlsx
+++ b/results/VI and heur scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\research\umich\mpt\pilot\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22561727-6244-48B1-9AD5-C6D58976B479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4B8750-3952-4F07-B22F-A8591637060F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2FE0DFFB-5825-496F-895C-1859655CAA03}"/>
   </bookViews>
@@ -41,15 +41,9 @@
     <t>central_adj</t>
   </si>
   <si>
-    <t>p1</t>
-  </si>
-  <si>
     <t>p2</t>
   </si>
   <si>
-    <t>p3</t>
-  </si>
-  <si>
     <t>p4</t>
   </si>
   <si>
@@ -71,10 +65,16 @@
     <t>VI</t>
   </si>
   <si>
-    <t>VI fixed b</t>
-  </si>
-  <si>
     <t>sigma</t>
+  </si>
+  <si>
+    <t>VI policy trained with constant belief</t>
+  </si>
+  <si>
+    <t>static E utility optimization on next year returns not updating the belief</t>
+  </si>
+  <si>
+    <t>E utility optimization on final timestep updating the belief probability on the scenarios</t>
   </si>
 </sst>
 </file>
@@ -446,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7E96E1-0FC4-40D4-A09A-CDB2A6C587CB}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="1"/>
@@ -454,48 +454,48 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
+      <c r="M3" t="s">
         <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -562,7 +562,7 @@
         <v>3.75</v>
       </c>
       <c r="I5">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="J5">
         <v>3.75</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>2.5299999999999998</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="F6">
         <v>1.8</v>
@@ -594,7 +594,7 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="I6">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="J6">
         <v>2.6</v>
@@ -614,7 +614,7 @@
         <v>20</v>
       </c>
       <c r="E7">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="F7">
         <v>1.41</v>
@@ -626,7 +626,7 @@
         <v>1.78</v>
       </c>
       <c r="I7">
-        <v>2.06</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="J7">
         <v>2.02</v>
@@ -638,7 +638,7 @@
         <v>1.8</v>
       </c>
       <c r="O7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -673,7 +673,264 @@
         <v>0.96899999999999997</v>
       </c>
     </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>8.31</v>
+      </c>
+      <c r="F9">
+        <v>8.31</v>
+      </c>
+      <c r="G9">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="H9">
+        <v>8.31</v>
+      </c>
+      <c r="I9">
+        <v>8.32</v>
+      </c>
+      <c r="J9">
+        <v>8.31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.2</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>5.65</v>
+      </c>
+      <c r="F10">
+        <v>5.48</v>
+      </c>
+      <c r="G10">
+        <v>5.47</v>
+      </c>
+      <c r="H10">
+        <v>5.65</v>
+      </c>
+      <c r="I10">
+        <v>5.65</v>
+      </c>
+      <c r="J10">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>3.8</v>
+      </c>
+      <c r="F11">
+        <v>2.71</v>
+      </c>
+      <c r="G11">
+        <v>2.71</v>
+      </c>
+      <c r="H11">
+        <v>3.81</v>
+      </c>
+      <c r="I11">
+        <v>3.81</v>
+      </c>
+      <c r="J11">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.2</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>2.84</v>
+      </c>
+      <c r="F12">
+        <v>1.82</v>
+      </c>
+      <c r="G12">
+        <v>1.82</v>
+      </c>
+      <c r="H12">
+        <v>2.85</v>
+      </c>
+      <c r="I12">
+        <v>2.87</v>
+      </c>
+      <c r="J12">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.1</v>
+      </c>
+      <c r="C13">
+        <v>1.2</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>5.7</v>
+      </c>
+      <c r="F13">
+        <v>3.79</v>
+      </c>
+      <c r="G13">
+        <v>3.83</v>
+      </c>
+      <c r="H13">
+        <v>5.62</v>
+      </c>
+      <c r="I13">
+        <v>5.72</v>
+      </c>
+      <c r="J13">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>0.1</v>
+      </c>
+      <c r="C14">
+        <v>1.2</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>4.05</v>
+      </c>
+      <c r="F14">
+        <v>2.62</v>
+      </c>
+      <c r="G14">
+        <v>2.62</v>
+      </c>
+      <c r="H14">
+        <v>4.04</v>
+      </c>
+      <c r="I14">
+        <v>4.05</v>
+      </c>
+      <c r="J14">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>0.1</v>
+      </c>
+      <c r="C15">
+        <v>1.2</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>2.94</v>
+      </c>
+      <c r="F15">
+        <v>1.94</v>
+      </c>
+      <c r="G15">
+        <v>1.94</v>
+      </c>
+      <c r="H15">
+        <v>2.94</v>
+      </c>
+      <c r="I15">
+        <v>2.94</v>
+      </c>
+      <c r="J15">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>0.1</v>
+      </c>
+      <c r="C16">
+        <v>1.2</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="F16">
+        <v>1.66</v>
+      </c>
+      <c r="G16">
+        <v>1.65</v>
+      </c>
+      <c r="H16">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="I16">
+        <v>2.44</v>
+      </c>
+      <c r="J16">
+        <v>2.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>